--- a/data/employees/EMP048/AST-EMP048-06.xlsx
+++ b/data/employees/EMP048/AST-EMP048-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Resource Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,210 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Project Resource Tracker - Jamie Brown (Engineering)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Engineer | Location: Fremont | Date: 2025-03-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Resources</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Proj Alpha</t>
+          <t>EMP048</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp048 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>81</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proj Beta</t>
+          <t>EMP048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2 - Build</t>
+          <t>Ast Emp048 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team B</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Proj Gamma</t>
+          <t>EMP048</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp048 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team C</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>74</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proj Delta</t>
+          <t>EMP048</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3 - Test</t>
+          <t>Ast Emp048 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>At Risk</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>65</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>74</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>87</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>85</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>97</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>73</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>93</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>73</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>73</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>61</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>75</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp048 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>76</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP048</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP048 contributes to ast emp048 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>